--- a/data/ready_stocks/logos-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,13 +418,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B2" t="str">
-        <v>LB-SS240130-White-8</v>
+        <v>LB-P220110-ArielKOMP-40</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -432,7 +432,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B3" t="str">
-        <v>LB-SS240130-Milk-8</v>
+        <v>LB-P220110-ArielOSN-40</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -446,7 +446,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B4" t="str">
-        <v>LB-SS240130-Beige-8</v>
+        <v>LB-P220110-AviaKOMP-40</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -460,13 +460,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B5" t="str">
-        <v>LB-SS240130-LightBlue-8</v>
+        <v>LB-P220110-AviaOSN-40</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -474,13 +474,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B6" t="str">
-        <v>LB-SS240130-MilkShokolad-8</v>
+        <v>LB-P220110-BalerinaKOMP-40</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -488,13 +488,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B7" t="str">
-        <v>LB-SS240130-GorkShokolad-8</v>
+        <v>LB-P220110-BalerinaOSN-40</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -502,7 +502,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B8" t="str">
-        <v>LB-SS240130-DimRoza-8</v>
+        <v>LB-P220110-BarbiKOMP-40</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -516,13 +516,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B9" t="str">
-        <v>LB-SS240130-Gray-8</v>
+        <v>LB-P220110-BarbiOSN-40</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -530,7 +530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B10" t="str">
-        <v>LB-SS240130-Oliva-8</v>
+        <v>LB-P220110-DinorobotyKOMP-40</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -544,7 +544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B11" t="str">
-        <v>LB-SS240130-SirenTuman-8</v>
+        <v>LB-P220110-DinorobotyOSN-40</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B12" t="str">
-        <v>LB-SS240130-Graphit-8</v>
+        <v>LB-P220110-EkspressKOMP-40</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -572,18 +572,1362 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B13" t="str">
-        <v>LB-SS240130-Indigo-9</v>
+        <v>LB-P220110-EkspressOSN-40</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B14" t="str">
+        <v>LB-P220110-FelixKOMP-40</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B15" t="str">
+        <v>LB-P220110-FelixOSN-40</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B16" t="str">
+        <v>LB-P220110-IskorkaKOMP-40</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B17" t="str">
+        <v>LB-P220110-IskorkaOSN-40</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B18" t="str">
+        <v>LB-P220110-KoshkiKOMP-40</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B19" t="str">
+        <v>LB-P220110-KoshkiOSN-40</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B20" t="str">
+        <v>LB-P220110-KosmicheskiyKorablKOMP-40</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B21" t="str">
+        <v>LB-P220110-KosmicheskiyKorablOSN-40</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B22" t="str">
+        <v>LB-P220110-KosmonavtyKOMP-40</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B23" t="str">
+        <v>LB-P220110-KosmonavtyOSN-40</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B24" t="str">
+        <v>LB-P220110-KruizKOMP-40</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B25" t="str">
+        <v>LB-P220110-KruizOSN-40</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B26" t="str">
+        <v>LB-P220110-MalenkayaPrincessaKOMP-40</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B27" t="str">
+        <v>LB-P220110-MalenkayaPrincessaOSN-40</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B28" t="str">
+        <v>LB-P220110-ModnitsyOSN-40</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B29" t="str">
+        <v>LB-P220110-MopsyGolyboiKOMP-40</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>LB-P220110-MopsyOSN-40</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B31" t="str">
+        <v>LB-P220110-MurlykaKOMP-40</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>LB-P220110-MurlykaOSN-40</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B33" t="str">
+        <v>LB-P220110-NochnoyDozorKOMP-40</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B34" t="str">
+        <v>LB-P220110-NochnoyDozorOSN-40</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B35" t="str">
+        <v>LB-P220110-PrintsessyKOMP-40</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B36" t="str">
+        <v>LB-P220110-PrintsessyOSN-40</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>LB-P220110-PuteshestvieOSN-40</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B38" t="str">
+        <v>LB-P220110-RybolovyKOMP-40</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B39" t="str">
+        <v>LB-P220110-RybolovyOSN-40</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B40" t="str">
+        <v>LB-P220110-SamoletyKOMP-40</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B41" t="str">
+        <v>LB-P220110-SamoletyOSN-40</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B42" t="str">
+        <v>LB-P220110-SledopytyOSN-40</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B43" t="str">
+        <v>LB-P220110-SovyataSerKOMP-40</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B44" t="str">
+        <v>LB-P220110-SovyataSerOSN-40</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B45" t="str">
+        <v>LB-P220110-SovyataZheltKOMP-40</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B46" t="str">
+        <v>LB-P220110-SovyataZheltOSN-40</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B47" t="str">
+        <v>LB-P220110-SpeedKOMP-40</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B48" t="str">
+        <v>LB-P220110-SpeedOSN-40</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>LB-P220110-SportOSN-40</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B50" t="str">
+        <v>LB-P220110-TaksyKOMP-40</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B51" t="str">
+        <v>LB-P220110-TaksyOSN-40</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B52" t="str">
+        <v>LB-P220110-TanetsKOMP-40</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B53" t="str">
+        <v>LB-P220110-TanetsOSN-40</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B54" t="str">
+        <v>LB-P220110-TsapTsarapKOMP-40</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B55" t="str">
+        <v>LB-P220110-TsapTsarapOSN-40</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B56" t="str">
+        <v>LB-P220110-YunyyStrotelKOMP-40</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B57" t="str">
+        <v>LB-P220110-YunyyStrotelOSN-40</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B58" t="str">
+        <v>LB-P220110-AmaliyaKOMP-40</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B59" t="str">
+        <v>LB-P220110-AmaliyaOSN-40</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B60" t="str">
+        <v>LB-P220110-ArabskayaNochKOMP-40</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B61" t="str">
+        <v>LB-P220110-ArabskayaNochOSN-40</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B62" t="str">
+        <v>LB-P220110-BellaYellowOSN-40</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B63" t="str">
+        <v>LB-P220110-BertaKOMP-40</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B64" t="str">
+        <v>LB-P220110-BertaOSN-40</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B65" t="str">
+        <v>LB-P220110-DerevoZhelaniyKOMP-40</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B66" t="str">
+        <v>LB-P220110-DerevoZhelaniyOSN-40</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B67" t="str">
+        <v>LB-P220110-DerevyaKOMP-40</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B68" t="str">
+        <v>LB-P220110-DerevyaOSN-40</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B69" t="str">
+        <v>LB-P220110-EdemGrayOSN-40</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B70" t="str">
+        <v>LB-P220110-Gerbariy(BellaYellow)KOMP-40</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B71" t="str">
+        <v>LB-P220110-GerbariyOSN-40</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B72" t="str">
+        <v>LB-P220110-GortenziyaOSN-40</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B73" t="str">
+        <v>LB-P220110-IzmerenieKOMP-40</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B74" t="str">
+        <v>LB-P220110-IzmerenieOSN-40</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B75" t="str">
+        <v>LB-P220110-KaktusyGrayKOMP-40</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B76" t="str">
+        <v>LB-P220110-KaktusyGrayOSN-40</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B77" t="str">
+        <v>LB-P220110-KaktusyKOMP-40</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B78" t="str">
+        <v>LB-P220110-KaktusyOSN-40</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B79" t="str">
+        <v>LB-P220110-Kletka-40</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B80" t="str">
+        <v>LB-P220110-KletkaBrownAOSN-40</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B81" t="str">
+        <v>LB-P220110-KletkaBrownBKOMP-40</v>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B82" t="str">
+        <v>LB-P220110-KletkaGrayAOSN-40</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B83" t="str">
+        <v>LB-P220110-KletkaGrayBKOMP-40</v>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B84" t="str">
+        <v>LB-P220110-KristiKOMP-40</v>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B85" t="str">
+        <v>LB-P220110-KristiOSN-40</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B86" t="str">
+        <v>LB-P220110-LastochkiOSN-40</v>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B87" t="str">
+        <v>LB-P220110-LauraOSN-40</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B88" t="str">
+        <v>LB-P220110-LuizaKOMP-40</v>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B89" t="str">
+        <v>LB-P220110-LuizaOSN-40</v>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B90" t="str">
+        <v>LB-P220110-MayskiyDenKOMP-40</v>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B91" t="str">
+        <v>LB-P220110-MayskiyDenOSN-40</v>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B92" t="str">
+        <v>LB-P220110-OazisGrayOSN-40</v>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B93" t="str">
+        <v>LB-P220110-OazisOlivaKOMP-40</v>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B94" t="str">
+        <v>LB-P220110-PaporotnikBirAOSN-40</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>LB-P220110-PaporotnikBirBKOMP-40</v>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B96" t="str">
+        <v>LB-P220110-PaporotnikGrayAOSN-40</v>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B97" t="str">
+        <v>LB-P220110-PaporotnikGrayBKOMP-40</v>
+      </c>
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B98" t="str">
+        <v>LB-P220110-SansaKOMP-40</v>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>LB-P220110-SansaOSN-40</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B100" t="str">
+        <v>LB-P220110-SimonaKOMP-40</v>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B101" t="str">
+        <v>LB-P220110-SimonaOSN-40</v>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>LB-P220110-ViveyaKOMP-40</v>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>LB-P220110-ViveyaOSN-40</v>
+      </c>
+      <c r="C103" t="str">
+        <v/>
+      </c>
+      <c r="D103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>LB-P220110-ZvezdnyyBrownBKOMP-40</v>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>LB-P220110-ZvezdnyyOSN-40</v>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>LB-P220110-ZvezNeboGrayAOSN-40</v>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>LB-P220110-SledopytyKOMP-40</v>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B108" t="str">
+        <v>LB-P220110-BellaPinkOSN-40</v>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>LB-P220110-ZvezdnoeNeboKOMP-40</v>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/logos-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-ozon-stocks-updated.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1600,7 +1600,7 @@
         <v/>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">

--- a/data/ready_stocks/logos-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,7 +418,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B2" t="str">
-        <v>LB-P220110-ArielKOMP-40</v>
+        <v>LTP-220110-PP-40-ArielOSN</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -432,7 +432,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B3" t="str">
-        <v>LB-P220110-ArielOSN-40</v>
+        <v>LTP-220110-PP-40-AviaKOMP</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -446,7 +446,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B4" t="str">
-        <v>LB-P220110-AviaKOMP-40</v>
+        <v>LTP-220110-PP-40-AviaOSN</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -460,13 +460,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B5" t="str">
-        <v>LB-P220110-AviaOSN-40</v>
+        <v>LTP-220110-PP-40-BalerinaKOMP</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -474,7 +474,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B6" t="str">
-        <v>LB-P220110-BalerinaKOMP-40</v>
+        <v>LTP-220110-PP-40-BalerinaOSN</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -488,13 +488,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B7" t="str">
-        <v>LB-P220110-BalerinaOSN-40</v>
+        <v>LTP-220110-PP-40-BarbiKOMP</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -502,7 +502,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B8" t="str">
-        <v>LB-P220110-BarbiKOMP-40</v>
+        <v>LTP-220110-PP-40-BarbiOSN</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -516,7 +516,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B9" t="str">
-        <v>LB-P220110-BarbiOSN-40</v>
+        <v>LTP-220110-PP-40-DinorobotyKOMP</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -530,7 +530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B10" t="str">
-        <v>LB-P220110-DinorobotyKOMP-40</v>
+        <v>LTP-220110-PP-40-DinorobotyOSN</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -544,7 +544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B11" t="str">
-        <v>LB-P220110-DinorobotyOSN-40</v>
+        <v>LTP-220110-PP-40-EkspressKOMP</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B12" t="str">
-        <v>LB-P220110-EkspressKOMP-40</v>
+        <v>LTP-220110-PP-40-EkspressOSN</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -572,7 +572,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B13" t="str">
-        <v>LB-P220110-EkspressOSN-40</v>
+        <v>LTP-220110-PP-40-FelixKOMP</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B14" t="str">
-        <v>LB-P220110-FelixKOMP-40</v>
+        <v>LTP-220110-PP-40-FelixOSN</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -600,7 +600,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B15" t="str">
-        <v>LB-P220110-FelixOSN-40</v>
+        <v>LTP-220110-PP-40-IskorkaKOMP</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -614,7 +614,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B16" t="str">
-        <v>LB-P220110-IskorkaKOMP-40</v>
+        <v>LTP-220110-PP-40-IskorkaOSN</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -628,7 +628,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B17" t="str">
-        <v>LB-P220110-IskorkaOSN-40</v>
+        <v>LTP-220110-PP-40-KoshkiKOMP</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B18" t="str">
-        <v>LB-P220110-KoshkiKOMP-40</v>
+        <v>LTP-220110-PP-40-KoshkiOSN</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -656,13 +656,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B19" t="str">
-        <v>LB-P220110-KoshkiOSN-40</v>
+        <v>LTP-220110-PP-40-KosmicheskiyKorablKOMP</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -670,7 +670,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B20" t="str">
-        <v>LB-P220110-KosmicheskiyKorablKOMP-40</v>
+        <v>LTP-220110-PP-40-KosmicheskiyKorablOSN</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -684,13 +684,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B21" t="str">
-        <v>LB-P220110-KosmicheskiyKorablOSN-40</v>
+        <v>LTP-220110-PP-40-KosmonavtyKOMP</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -698,7 +698,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B22" t="str">
-        <v>LB-P220110-KosmonavtyKOMP-40</v>
+        <v>LTP-220110-PP-40-KosmonavtyOSN</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -712,7 +712,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B23" t="str">
-        <v>LB-P220110-KosmonavtyOSN-40</v>
+        <v>LTP-220110-PP-40-KruizKOMP</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B24" t="str">
-        <v>LB-P220110-KruizKOMP-40</v>
+        <v>LTP-220110-PP-40-KruizOSN</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -740,7 +740,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B25" t="str">
-        <v>LB-P220110-KruizOSN-40</v>
+        <v>LTP-220110-PP-40-MalenkayaPrincessaKOMP</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -754,7 +754,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B26" t="str">
-        <v>LB-P220110-MalenkayaPrincessaKOMP-40</v>
+        <v>LTP-220110-PP-40-MalenkayaPrincessaOSN</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B27" t="str">
-        <v>LB-P220110-MalenkayaPrincessaOSN-40</v>
+        <v>LTP-220110-PP-40-ModnitsyOSN</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -782,7 +782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B28" t="str">
-        <v>LB-P220110-ModnitsyOSN-40</v>
+        <v>LTP-220110-PP-40-MopsyGolyboiKOMP</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B29" t="str">
-        <v>LB-P220110-MopsyGolyboiKOMP-40</v>
+        <v>LTP-220110-PP-40-MopsyOSN</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -810,7 +810,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B30" t="str">
-        <v>LB-P220110-MopsyOSN-40</v>
+        <v>LTP-220110-PP-40-MurlykaKOMP</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -824,7 +824,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B31" t="str">
-        <v>LB-P220110-MurlykaKOMP-40</v>
+        <v>LTP-220110-PP-40-MurlykaOSN</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -838,13 +838,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B32" t="str">
-        <v>LB-P220110-MurlykaOSN-40</v>
+        <v>LTP-220110-PP-40-NochnoyDozorKOMP</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -852,7 +852,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B33" t="str">
-        <v>LB-P220110-NochnoyDozorKOMP-40</v>
+        <v>LTP-220110-PP-40-NochnoyDozorOSN</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B34" t="str">
-        <v>LB-P220110-NochnoyDozorOSN-40</v>
+        <v>LTP-220110-PP-40-PrintsessyKOMP</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -880,7 +880,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B35" t="str">
-        <v>LB-P220110-PrintsessyKOMP-40</v>
+        <v>LTP-220110-PP-40-PrintsessyOSN</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -894,13 +894,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B36" t="str">
-        <v>LB-P220110-PrintsessyOSN-40</v>
+        <v>LTP-220110-PP-40-PuteshestvieOSN</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -908,13 +908,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B37" t="str">
-        <v>LB-P220110-PuteshestvieOSN-40</v>
+        <v>LTP-220110-PP-40-RybolovyKOMP</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -922,7 +922,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B38" t="str">
-        <v>LB-P220110-RybolovyKOMP-40</v>
+        <v>LTP-220110-PP-40-RybolovyOSN</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B39" t="str">
-        <v>LB-P220110-RybolovyOSN-40</v>
+        <v>LTP-220110-PP-40-SamoletyKOMP</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -950,7 +950,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B40" t="str">
-        <v>LB-P220110-SamoletyKOMP-40</v>
+        <v>LTP-220110-PP-40-SamoletyOSN</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -964,7 +964,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B41" t="str">
-        <v>LB-P220110-SamoletyOSN-40</v>
+        <v>LTP-220110-PP-40-SledopytyOSN</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -978,7 +978,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B42" t="str">
-        <v>LB-P220110-SledopytyOSN-40</v>
+        <v>LTP-220110-PP-40-SovyataSerKOMP</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -992,7 +992,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B43" t="str">
-        <v>LB-P220110-SovyataSerKOMP-40</v>
+        <v>LTP-220110-PP-40-SovyataSerOSN</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1006,7 +1006,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B44" t="str">
-        <v>LB-P220110-SovyataSerOSN-40</v>
+        <v>LTP-220110-PP-40-SovyataZheltKOMP</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1020,13 +1020,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B45" t="str">
-        <v>LB-P220110-SovyataZheltKOMP-40</v>
+        <v>LTP-220110-PP-40-SovyataZheltOSN</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1034,13 +1034,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B46" t="str">
-        <v>LB-P220110-SovyataZheltOSN-40</v>
+        <v>LTP-220110-PP-40-SpeedKOMP</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -1048,7 +1048,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B47" t="str">
-        <v>LB-P220110-SpeedKOMP-40</v>
+        <v>LTP-220110-PP-40-SpeedOSN</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1062,7 +1062,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B48" t="str">
-        <v>LB-P220110-SpeedOSN-40</v>
+        <v>LTP-220110-PP-40-SportOSN</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B49" t="str">
-        <v>LB-P220110-SportOSN-40</v>
+        <v>LTP-220110-PP-40-TaksyKOMP</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1090,7 +1090,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B50" t="str">
-        <v>LB-P220110-TaksyKOMP-40</v>
+        <v>LTP-220110-PP-40-TaksyOSN</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1104,7 +1104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B51" t="str">
-        <v>LB-P220110-TaksyOSN-40</v>
+        <v>LTP-220110-PP-40-TanetsKOMP</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1118,7 +1118,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B52" t="str">
-        <v>LB-P220110-TanetsKOMP-40</v>
+        <v>LTP-220110-PP-40-TanetsOSN</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B53" t="str">
-        <v>LB-P220110-TanetsOSN-40</v>
+        <v>LTP-220110-PP-40-TsapTsarapKOMP</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1146,7 +1146,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B54" t="str">
-        <v>LB-P220110-TsapTsarapKOMP-40</v>
+        <v>LTP-220110-PP-40-TsapTsarapOSN</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1160,7 +1160,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B55" t="str">
-        <v>LB-P220110-TsapTsarapOSN-40</v>
+        <v>LTP-220110-PP-40-YunyyStrotelKOMP</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1174,7 +1174,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B56" t="str">
-        <v>LB-P220110-YunyyStrotelKOMP-40</v>
+        <v>LTP-220110-PP-40-YunyyStrotelOSN</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1188,7 +1188,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B57" t="str">
-        <v>LB-P220110-YunyyStrotelOSN-40</v>
+        <v>LTP-220110-PP-40-AmaliyaKOMP</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1202,7 +1202,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B58" t="str">
-        <v>LB-P220110-AmaliyaKOMP-40</v>
+        <v>LTP-220110-PP-40-AmaliyaOSN</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1216,7 +1216,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B59" t="str">
-        <v>LB-P220110-AmaliyaOSN-40</v>
+        <v>LTP-220110-PP-40-ArabskayaNochKOMP</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1230,7 +1230,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B60" t="str">
-        <v>LB-P220110-ArabskayaNochKOMP-40</v>
+        <v>LTP-220110-PP-40-ArabskayaNochOSN</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1244,7 +1244,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B61" t="str">
-        <v>LB-P220110-ArabskayaNochOSN-40</v>
+        <v>LTP-220110-PP-40-BellaYellowOSN</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1258,13 +1258,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B62" t="str">
-        <v>LB-P220110-BellaYellowOSN-40</v>
+        <v>LTP-220110-PP-40-BertaKOMP</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1272,13 +1272,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B63" t="str">
-        <v>LB-P220110-BertaKOMP-40</v>
+        <v>LTP-220110-PP-40-BertaOSN</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1286,13 +1286,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B64" t="str">
-        <v>LB-P220110-BertaOSN-40</v>
+        <v>LTP-220110-PP-40-DerevoZhelaniyKOMP</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -1300,7 +1300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B65" t="str">
-        <v>LB-P220110-DerevoZhelaniyKOMP-40</v>
+        <v>LTP-220110-PP-40-DerevoZhelaniyOSN</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1314,7 +1314,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B66" t="str">
-        <v>LB-P220110-DerevoZhelaniyOSN-40</v>
+        <v>LTP-220110-PP-40-DerevyaKOMP</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1328,7 +1328,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B67" t="str">
-        <v>LB-P220110-DerevyaKOMP-40</v>
+        <v>LTP-220110-PP-40-DerevyaOSN</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1342,7 +1342,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B68" t="str">
-        <v>LB-P220110-DerevyaOSN-40</v>
+        <v>LTP-220110-PP-40-EdemGrayOSN</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B69" t="str">
-        <v>LB-P220110-EdemGrayOSN-40</v>
+        <v>LTP-220110-PP-40-Gerbariy(BellaYellow)KOMP</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1370,7 +1370,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B70" t="str">
-        <v>LB-P220110-Gerbariy(BellaYellow)KOMP-40</v>
+        <v>LTP-220110-PP-40-GerbariyOSN</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1384,13 +1384,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B71" t="str">
-        <v>LB-P220110-GerbariyOSN-40</v>
+        <v>LTP-220110-PP-40-GortenziyaOSN</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1398,7 +1398,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B72" t="str">
-        <v>LB-P220110-GortenziyaOSN-40</v>
+        <v>LTP-220110-PP-40-IzmerenieKOMP</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -1412,7 +1412,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B73" t="str">
-        <v>LB-P220110-IzmerenieKOMP-40</v>
+        <v>LTP-220110-PP-40-IzmerenieOSN</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -1426,7 +1426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B74" t="str">
-        <v>LB-P220110-IzmerenieOSN-40</v>
+        <v>LTP-220110-PP-40-KaktusyGrayKOMP</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1440,7 +1440,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B75" t="str">
-        <v>LB-P220110-KaktusyGrayKOMP-40</v>
+        <v>LTP-220110-PP-40-KaktusyGrayOSN</v>
       </c>
       <c r="C75" t="str">
         <v/>
@@ -1454,7 +1454,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B76" t="str">
-        <v>LB-P220110-KaktusyGrayOSN-40</v>
+        <v>LTP-220110-PP-40-KaktusyKOMP</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B77" t="str">
-        <v>LB-P220110-KaktusyKOMP-40</v>
+        <v>LTP-220110-PP-40-KaktusyOSN</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -1482,7 +1482,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B78" t="str">
-        <v>LB-P220110-KaktusyOSN-40</v>
+        <v>LTP-220110-PP-40-Kletka</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B79" t="str">
-        <v>LB-P220110-Kletka-40</v>
+        <v>LTP-220110-PP-40-KletkaBrownAOSN</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -1510,7 +1510,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B80" t="str">
-        <v>LB-P220110-KletkaBrownAOSN-40</v>
+        <v>LTP-220110-PP-40-KletkaBrownBKOMP</v>
       </c>
       <c r="C80" t="str">
         <v/>
@@ -1524,7 +1524,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B81" t="str">
-        <v>LB-P220110-KletkaBrownBKOMP-40</v>
+        <v>LTP-220110-PP-40-KletkaGrayAOSN</v>
       </c>
       <c r="C81" t="str">
         <v/>
@@ -1538,7 +1538,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B82" t="str">
-        <v>LB-P220110-KletkaGrayAOSN-40</v>
+        <v>LTP-220110-PP-40-KletkaGrayBKOMP</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B83" t="str">
-        <v>LB-P220110-KletkaGrayBKOMP-40</v>
+        <v>LTP-220110-PP-40-KristiKOMP</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -1566,7 +1566,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B84" t="str">
-        <v>LB-P220110-KristiKOMP-40</v>
+        <v>LTP-220110-PP-40-KristiOSN</v>
       </c>
       <c r="C84" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B85" t="str">
-        <v>LB-P220110-KristiOSN-40</v>
+        <v>LTP-220110-PP-40-LastochkiOSN</v>
       </c>
       <c r="C85" t="str">
         <v/>
@@ -1594,7 +1594,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B86" t="str">
-        <v>LB-P220110-LastochkiOSN-40</v>
+        <v>LTP-220110-PP-40-LauraOSN</v>
       </c>
       <c r="C86" t="str">
         <v/>
@@ -1608,7 +1608,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B87" t="str">
-        <v>LB-P220110-LauraOSN-40</v>
+        <v>LTP-220110-PP-40-LuizaKOMP</v>
       </c>
       <c r="C87" t="str">
         <v/>
@@ -1622,7 +1622,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B88" t="str">
-        <v>LB-P220110-LuizaKOMP-40</v>
+        <v>LTP-220110-PP-40-LuizaOSN</v>
       </c>
       <c r="C88" t="str">
         <v/>
@@ -1636,7 +1636,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B89" t="str">
-        <v>LB-P220110-LuizaOSN-40</v>
+        <v>LTP-220110-PP-40-MayskiyDenKOMP</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1650,7 +1650,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B90" t="str">
-        <v>LB-P220110-MayskiyDenKOMP-40</v>
+        <v>LTP-220110-PP-40-MayskiyDenOSN</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -1664,7 +1664,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B91" t="str">
-        <v>LB-P220110-MayskiyDenOSN-40</v>
+        <v>LTP-220110-PP-40-OazisGrayOSN</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -1678,7 +1678,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B92" t="str">
-        <v>LB-P220110-OazisGrayOSN-40</v>
+        <v>LTP-220110-PP-40-OazisOlivaKOMP</v>
       </c>
       <c r="C92" t="str">
         <v/>
@@ -1692,7 +1692,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B93" t="str">
-        <v>LB-P220110-OazisOlivaKOMP-40</v>
+        <v>LTP-220110-PP-40-PaporotnikBirAOSN</v>
       </c>
       <c r="C93" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B94" t="str">
-        <v>LB-P220110-PaporotnikBirAOSN-40</v>
+        <v>LTP-220110-PP-40-PaporotnikBirBKOMP</v>
       </c>
       <c r="C94" t="str">
         <v/>
@@ -1720,7 +1720,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B95" t="str">
-        <v>LB-P220110-PaporotnikBirBKOMP-40</v>
+        <v>LTP-220110-PP-40-PaporotnikGrayAOSN</v>
       </c>
       <c r="C95" t="str">
         <v/>
@@ -1734,7 +1734,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B96" t="str">
-        <v>LB-P220110-PaporotnikGrayAOSN-40</v>
+        <v>LTP-220110-PP-40-PaporotnikGrayBKOMP</v>
       </c>
       <c r="C96" t="str">
         <v/>
@@ -1748,7 +1748,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B97" t="str">
-        <v>LB-P220110-PaporotnikGrayBKOMP-40</v>
+        <v>LTP-220110-PP-40-SansaKOMP</v>
       </c>
       <c r="C97" t="str">
         <v/>
@@ -1762,7 +1762,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B98" t="str">
-        <v>LB-P220110-SansaKOMP-40</v>
+        <v>LTP-220110-PP-40-SansaOSN</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B99" t="str">
-        <v>LB-P220110-SansaOSN-40</v>
+        <v>LTP-220110-PP-40-SimonaKOMP</v>
       </c>
       <c r="C99" t="str">
         <v/>
@@ -1790,7 +1790,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B100" t="str">
-        <v>LB-P220110-SimonaKOMP-40</v>
+        <v>LTP-220110-PP-40-SimonaOSN</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -1804,7 +1804,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B101" t="str">
-        <v>LB-P220110-SimonaOSN-40</v>
+        <v>LTP-220110-PP-40-ViveyaKOMP</v>
       </c>
       <c r="C101" t="str">
         <v/>
@@ -1818,7 +1818,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B102" t="str">
-        <v>LB-P220110-ViveyaKOMP-40</v>
+        <v>LTP-220110-PP-40-ViveyaOSN</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B103" t="str">
-        <v>LB-P220110-ViveyaOSN-40</v>
+        <v>LTP-220110-PP-40-ZvezdnyyBrownBKOMP</v>
       </c>
       <c r="C103" t="str">
         <v/>
@@ -1846,13 +1846,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B104" t="str">
-        <v>LB-P220110-ZvezdnyyBrownBKOMP-40</v>
+        <v>LTP-220110-PP-40-ZvezdnyyOSN</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1860,13 +1860,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B105" t="str">
-        <v>LB-P220110-ZvezdnyyOSN-40</v>
+        <v>LTP-220110-PP-40-ZvezNeboGrayAOSN</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -1874,7 +1874,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B106" t="str">
-        <v>LB-P220110-ZvezNeboGrayAOSN-40</v>
+        <v>LTP-220110-PP-40-SledopytyKOMP</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -1888,13 +1888,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B107" t="str">
-        <v>LB-P220110-SledopytyKOMP-40</v>
+        <v>LTP-220110-PP-40-BellaPinkOSN</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1902,13 +1902,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B108" t="str">
-        <v>LB-P220110-BellaPinkOSN-40</v>
+        <v>LTP-220110-PP-40-ZvezdnoeNeboKOMP</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -1916,18 +1916,452 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B109" t="str">
-        <v>LB-P220110-ZvezdnoeNeboKOMP-40</v>
+        <v>LTP-240130-SST-8-Milk</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109">
         <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B110" t="str">
+        <v>LTP-220115-M-PP-8-Gray</v>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+      <c r="D110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B111" t="str">
+        <v>LTP-220115-M-PP-8-Coffee</v>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>LTP-220115-M-PP-8-GrayGreen</v>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>LTP-220115-M-PP-8-Brusnik</v>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B114" t="str">
+        <v>LTP-220115-M-PP-8-Gorchica</v>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B115" t="str">
+        <v>LTP-220115-M-PP-8-Pudra</v>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B116" t="str">
+        <v>LTP-220115-M-PP-8-Persik</v>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B117" t="str">
+        <v>LTP-220115-M-PP-8-Baklazhan</v>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B118" t="str">
+        <v>LTP-220115-M-PP-8-GrayBlue</v>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B119" t="str">
+        <v>LTP-220115-M-PP-8-Grafit</v>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B120" t="str">
+        <v>LTP-220115-M-PP-8-Terrakot</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>LTP-220115-M-PP-8-LightPink</v>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B122" t="str">
+        <v>LTP-220115-M-PP-8-Mint</v>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>LTP-220115-M-PP-8-Tifani</v>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>LTP-220115-M-PP-8-DymchatayaRoza</v>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>LTP-220115-M-PP-8-Oliva</v>
+      </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>LTP-220115-M-PP-8-LightBlue</v>
+      </c>
+      <c r="C126" t="str">
+        <v/>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B127" t="str">
+        <v>LTP-220115-M-PP-8-Beige</v>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B128" t="str">
+        <v>LTP-220115-M-PP-8-Latte</v>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B129" t="str">
+        <v>LTP-220115-M-PP-8-White</v>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B130" t="str">
+        <v>LTP-240130-SST-8-Graphit</v>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B131" t="str">
+        <v>LTP-240130-SST-8-GorkShokolad</v>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B132" t="str">
+        <v>LTP-240130-SST-8-Indigo</v>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B133" t="str">
+        <v>LTP-220115-M-PP-8-Milk</v>
+      </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B134" t="str">
+        <v>LTP-240130-SST-8-Gray</v>
+      </c>
+      <c r="C134" t="str">
+        <v/>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B135" t="str">
+        <v>LTP-240130-SST-8-MilkShokolad</v>
+      </c>
+      <c r="C135" t="str">
+        <v/>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B136" t="str">
+        <v>LTP-240130-SST-8-Beige</v>
+      </c>
+      <c r="C136" t="str">
+        <v/>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B137" t="str">
+        <v>LTP-240130-SST-8-LightBlue</v>
+      </c>
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B138" t="str">
+        <v>LTP-240130-SST-8-Oliva</v>
+      </c>
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B139" t="str">
+        <v>LTP-240130-SST-8-DimRoza</v>
+      </c>
+      <c r="C139" t="str">
+        <v/>
+      </c>
+      <c r="D139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B140" t="str">
+        <v>LTP-240130-SST-8-SirenTuman</v>
+      </c>
+      <c r="C140" t="str">
+        <v/>
+      </c>
+      <c r="D140">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/logos-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,7 +418,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B2" t="str">
-        <v>LTP-220110-PP-40-ArielOSN</v>
+        <v>LTP-220110-PP-40-ArielKOMP</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -432,7 +432,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B3" t="str">
-        <v>LTP-220110-PP-40-AviaKOMP</v>
+        <v>LTP-220110-PP-40-ArielOSN</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -446,7 +446,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B4" t="str">
-        <v>LTP-220110-PP-40-AviaOSN</v>
+        <v>LTP-220110-PP-40-AviaKOMP</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -460,13 +460,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B5" t="str">
-        <v>LTP-220110-PP-40-BalerinaKOMP</v>
+        <v>LTP-220110-PP-40-AviaOSN</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -474,7 +474,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B6" t="str">
-        <v>LTP-220110-PP-40-BalerinaOSN</v>
+        <v>LTP-220110-PP-40-BalerinaKOMP</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -488,7 +488,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B7" t="str">
-        <v>LTP-220110-PP-40-BarbiKOMP</v>
+        <v>LTP-220110-PP-40-BalerinaOSN</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -502,7 +502,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B8" t="str">
-        <v>LTP-220110-PP-40-BarbiOSN</v>
+        <v>LTP-220110-PP-40-BarbiKOMP</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -516,7 +516,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B9" t="str">
-        <v>LTP-220110-PP-40-DinorobotyKOMP</v>
+        <v>LTP-220110-PP-40-BarbiOSN</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -530,7 +530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B10" t="str">
-        <v>LTP-220110-PP-40-DinorobotyOSN</v>
+        <v>LTP-220110-PP-40-DinorobotyKOMP</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -544,7 +544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B11" t="str">
-        <v>LTP-220110-PP-40-EkspressKOMP</v>
+        <v>LTP-220110-PP-40-DinorobotyOSN</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B12" t="str">
-        <v>LTP-220110-PP-40-EkspressOSN</v>
+        <v>LTP-220110-PP-40-EkspressKOMP</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -572,7 +572,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B13" t="str">
-        <v>LTP-220110-PP-40-FelixKOMP</v>
+        <v>LTP-220110-PP-40-EkspressOSN</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B14" t="str">
-        <v>LTP-220110-PP-40-FelixOSN</v>
+        <v>LTP-220110-PP-40-FelixKOMP</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -600,7 +600,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B15" t="str">
-        <v>LTP-220110-PP-40-IskorkaKOMP</v>
+        <v>LTP-220110-PP-40-FelixOSN</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -614,7 +614,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B16" t="str">
-        <v>LTP-220110-PP-40-IskorkaOSN</v>
+        <v>LTP-220110-PP-40-IskorkaKOMP</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -628,7 +628,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B17" t="str">
-        <v>LTP-220110-PP-40-KoshkiKOMP</v>
+        <v>LTP-220110-PP-40-IskorkaOSN</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B18" t="str">
-        <v>LTP-220110-PP-40-KoshkiOSN</v>
+        <v>LTP-220110-PP-40-KoshkiKOMP</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -656,13 +656,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B19" t="str">
-        <v>LTP-220110-PP-40-KosmicheskiyKorablKOMP</v>
+        <v>LTP-220110-PP-40-KoshkiOSN</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -670,7 +670,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B20" t="str">
-        <v>LTP-220110-PP-40-KosmicheskiyKorablOSN</v>
+        <v>LTP-220110-PP-40-KosmicheskiyKorablKOMP</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -684,13 +684,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B21" t="str">
-        <v>LTP-220110-PP-40-KosmonavtyKOMP</v>
+        <v>LTP-220110-PP-40-KosmicheskiyKorablOSN</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -698,7 +698,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B22" t="str">
-        <v>LTP-220110-PP-40-KosmonavtyOSN</v>
+        <v>LTP-220110-PP-40-KosmonavtyKOMP</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -712,7 +712,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B23" t="str">
-        <v>LTP-220110-PP-40-KruizKOMP</v>
+        <v>LTP-220110-PP-40-KosmonavtyOSN</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B24" t="str">
-        <v>LTP-220110-PP-40-KruizOSN</v>
+        <v>LTP-220110-PP-40-KruizKOMP</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -740,7 +740,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B25" t="str">
-        <v>LTP-220110-PP-40-MalenkayaPrincessaKOMP</v>
+        <v>LTP-220110-PP-40-KruizOSN</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -754,7 +754,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B26" t="str">
-        <v>LTP-220110-PP-40-MalenkayaPrincessaOSN</v>
+        <v>LTP-220110-PP-40-MalenkayaPrincessaKOMP</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B27" t="str">
-        <v>LTP-220110-PP-40-ModnitsyOSN</v>
+        <v>LTP-220110-PP-40-MalenkayaPrincessaOSN</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -782,7 +782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B28" t="str">
-        <v>LTP-220110-PP-40-MopsyGolyboiKOMP</v>
+        <v>LTP-220110-PP-40-ModnitsyOSN</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B29" t="str">
-        <v>LTP-220110-PP-40-MopsyOSN</v>
+        <v>LTP-220110-PP-40-MopsyGolyboiKOMP</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -810,7 +810,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B30" t="str">
-        <v>LTP-220110-PP-40-MurlykaKOMP</v>
+        <v>LTP-220110-PP-40-MopsyOSN</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -824,7 +824,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B31" t="str">
-        <v>LTP-220110-PP-40-MurlykaOSN</v>
+        <v>LTP-220110-PP-40-MurlykaKOMP</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -838,7 +838,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B32" t="str">
-        <v>LTP-220110-PP-40-NochnoyDozorKOMP</v>
+        <v>LTP-220110-PP-40-MurlykaOSN</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -852,7 +852,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B33" t="str">
-        <v>LTP-220110-PP-40-NochnoyDozorOSN</v>
+        <v>LTP-220110-PP-40-NochnoyDozorKOMP</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B34" t="str">
-        <v>LTP-220110-PP-40-PrintsessyKOMP</v>
+        <v>LTP-220110-PP-40-NochnoyDozorOSN</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -880,7 +880,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B35" t="str">
-        <v>LTP-220110-PP-40-PrintsessyOSN</v>
+        <v>LTP-220110-PP-40-PrintsessyKOMP</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -894,13 +894,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B36" t="str">
-        <v>LTP-220110-PP-40-PuteshestvieOSN</v>
+        <v>LTP-220110-PP-40-PrintsessyOSN</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -908,13 +908,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B37" t="str">
-        <v>LTP-220110-PP-40-RybolovyKOMP</v>
+        <v>LTP-220110-PP-40-PuteshestvieOSN</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -922,7 +922,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B38" t="str">
-        <v>LTP-220110-PP-40-RybolovyOSN</v>
+        <v>LTP-220110-PP-40-RybolovyKOMP</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B39" t="str">
-        <v>LTP-220110-PP-40-SamoletyKOMP</v>
+        <v>LTP-220110-PP-40-RybolovyOSN</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -950,7 +950,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B40" t="str">
-        <v>LTP-220110-PP-40-SamoletyOSN</v>
+        <v>LTP-220110-PP-40-SamoletyKOMP</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -964,7 +964,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B41" t="str">
-        <v>LTP-220110-PP-40-SledopytyOSN</v>
+        <v>LTP-220110-PP-40-SamoletyOSN</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -978,7 +978,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B42" t="str">
-        <v>LTP-220110-PP-40-SovyataSerKOMP</v>
+        <v>LTP-220110-PP-40-SledopytyOSN</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -992,7 +992,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B43" t="str">
-        <v>LTP-220110-PP-40-SovyataSerOSN</v>
+        <v>LTP-220110-PP-40-SovyataSerKOMP</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1006,7 +1006,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B44" t="str">
-        <v>LTP-220110-PP-40-SovyataZheltKOMP</v>
+        <v>LTP-220110-PP-40-SovyataSerOSN</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1020,13 +1020,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B45" t="str">
-        <v>LTP-220110-PP-40-SovyataZheltOSN</v>
+        <v>LTP-220110-PP-40-SovyataZheltKOMP</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -1034,13 +1034,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B46" t="str">
-        <v>LTP-220110-PP-40-SpeedKOMP</v>
+        <v>LTP-220110-PP-40-SovyataZheltOSN</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1048,7 +1048,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B47" t="str">
-        <v>LTP-220110-PP-40-SpeedOSN</v>
+        <v>LTP-220110-PP-40-SpeedKOMP</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1062,7 +1062,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B48" t="str">
-        <v>LTP-220110-PP-40-SportOSN</v>
+        <v>LTP-220110-PP-40-SpeedOSN</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B49" t="str">
-        <v>LTP-220110-PP-40-TaksyKOMP</v>
+        <v>LTP-220110-PP-40-SportOSN</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1090,7 +1090,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B50" t="str">
-        <v>LTP-220110-PP-40-TaksyOSN</v>
+        <v>LTP-220110-PP-40-TaksyKOMP</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1104,7 +1104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B51" t="str">
-        <v>LTP-220110-PP-40-TanetsKOMP</v>
+        <v>LTP-220110-PP-40-TaksyOSN</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1118,7 +1118,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B52" t="str">
-        <v>LTP-220110-PP-40-TanetsOSN</v>
+        <v>LTP-220110-PP-40-TanetsKOMP</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B53" t="str">
-        <v>LTP-220110-PP-40-TsapTsarapKOMP</v>
+        <v>LTP-220110-PP-40-TanetsOSN</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1146,7 +1146,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B54" t="str">
-        <v>LTP-220110-PP-40-TsapTsarapOSN</v>
+        <v>LTP-220110-PP-40-TsapTsarapKOMP</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1160,7 +1160,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B55" t="str">
-        <v>LTP-220110-PP-40-YunyyStrotelKOMP</v>
+        <v>LTP-220110-PP-40-TsapTsarapOSN</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1174,7 +1174,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B56" t="str">
-        <v>LTP-220110-PP-40-YunyyStrotelOSN</v>
+        <v>LTP-220110-PP-40-YunyyStrotelKOMP</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1188,7 +1188,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B57" t="str">
-        <v>LTP-220110-PP-40-AmaliyaKOMP</v>
+        <v>LTP-220110-PP-40-YunyyStrotelOSN</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1202,7 +1202,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B58" t="str">
-        <v>LTP-220110-PP-40-AmaliyaOSN</v>
+        <v>LTP-220110-PP-40-AmaliyaKOMP</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1216,7 +1216,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B59" t="str">
-        <v>LTP-220110-PP-40-ArabskayaNochKOMP</v>
+        <v>LTP-220110-PP-40-AmaliyaOSN</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1230,7 +1230,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B60" t="str">
-        <v>LTP-220110-PP-40-ArabskayaNochOSN</v>
+        <v>LTP-220110-PP-40-ArabskayaNochKOMP</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1244,7 +1244,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B61" t="str">
-        <v>LTP-220110-PP-40-BellaYellowOSN</v>
+        <v>LTP-220110-PP-40-ArabskayaNochOSN</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1258,13 +1258,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B62" t="str">
-        <v>LTP-220110-PP-40-BertaKOMP</v>
+        <v>LTP-220110-PP-40-BellaYellowOSN</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -1272,7 +1272,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B63" t="str">
-        <v>LTP-220110-PP-40-BertaOSN</v>
+        <v>LTP-220110-PP-40-BertaKOMP</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1286,13 +1286,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B64" t="str">
-        <v>LTP-220110-PP-40-DerevoZhelaniyKOMP</v>
+        <v>LTP-220110-PP-40-BertaOSN</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1300,7 +1300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B65" t="str">
-        <v>LTP-220110-PP-40-DerevoZhelaniyOSN</v>
+        <v>LTP-220110-PP-40-DerevoZhelaniyKOMP</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1314,7 +1314,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B66" t="str">
-        <v>LTP-220110-PP-40-DerevyaKOMP</v>
+        <v>LTP-220110-PP-40-DerevoZhelaniyOSN</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1328,7 +1328,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B67" t="str">
-        <v>LTP-220110-PP-40-DerevyaOSN</v>
+        <v>LTP-220110-PP-40-DerevyaKOMP</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1342,7 +1342,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B68" t="str">
-        <v>LTP-220110-PP-40-EdemGrayOSN</v>
+        <v>LTP-220110-PP-40-DerevyaOSN</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B69" t="str">
-        <v>LTP-220110-PP-40-Gerbariy(BellaYellow)KOMP</v>
+        <v>LTP-220110-PP-40-EdemGrayOSN</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1370,7 +1370,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B70" t="str">
-        <v>LTP-220110-PP-40-GerbariyOSN</v>
+        <v>LTP-220110-PP-40-Gerbariy(BellaYellow)KOMP</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1384,13 +1384,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B71" t="str">
-        <v>LTP-220110-PP-40-GortenziyaOSN</v>
+        <v>LTP-220110-PP-40-GerbariyOSN</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -1398,13 +1398,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B72" t="str">
-        <v>LTP-220110-PP-40-IzmerenieKOMP</v>
+        <v>LTP-220110-PP-40-GortenziyaOSN</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1412,7 +1412,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B73" t="str">
-        <v>LTP-220110-PP-40-IzmerenieOSN</v>
+        <v>LTP-220110-PP-40-IzmerenieKOMP</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -1426,7 +1426,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B74" t="str">
-        <v>LTP-220110-PP-40-KaktusyGrayKOMP</v>
+        <v>LTP-220110-PP-40-IzmerenieOSN</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1440,7 +1440,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B75" t="str">
-        <v>LTP-220110-PP-40-KaktusyGrayOSN</v>
+        <v>LTP-220110-PP-40-KaktusyGrayKOMP</v>
       </c>
       <c r="C75" t="str">
         <v/>
@@ -1454,7 +1454,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B76" t="str">
-        <v>LTP-220110-PP-40-KaktusyKOMP</v>
+        <v>LTP-220110-PP-40-KaktusyGrayOSN</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -1468,7 +1468,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B77" t="str">
-        <v>LTP-220110-PP-40-KaktusyOSN</v>
+        <v>LTP-220110-PP-40-KaktusyKOMP</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -1482,7 +1482,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B78" t="str">
-        <v>LTP-220110-PP-40-Kletka</v>
+        <v>LTP-220110-PP-40-KaktusyOSN</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B79" t="str">
-        <v>LTP-220110-PP-40-KletkaBrownAOSN</v>
+        <v>LTP-220110-PP-40-Kletka</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -1510,7 +1510,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B80" t="str">
-        <v>LTP-220110-PP-40-KletkaBrownBKOMP</v>
+        <v>LTP-220110-PP-40-KletkaBrownAOSN</v>
       </c>
       <c r="C80" t="str">
         <v/>
@@ -1524,7 +1524,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B81" t="str">
-        <v>LTP-220110-PP-40-KletkaGrayAOSN</v>
+        <v>LTP-220110-PP-40-KletkaBrownBKOMP</v>
       </c>
       <c r="C81" t="str">
         <v/>
@@ -1538,7 +1538,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B82" t="str">
-        <v>LTP-220110-PP-40-KletkaGrayBKOMP</v>
+        <v>LTP-220110-PP-40-KletkaGrayAOSN</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B83" t="str">
-        <v>LTP-220110-PP-40-KristiKOMP</v>
+        <v>LTP-220110-PP-40-KletkaGrayBKOMP</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -1566,7 +1566,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B84" t="str">
-        <v>LTP-220110-PP-40-KristiOSN</v>
+        <v>LTP-220110-PP-40-KristiKOMP</v>
       </c>
       <c r="C84" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B85" t="str">
-        <v>LTP-220110-PP-40-LastochkiOSN</v>
+        <v>LTP-220110-PP-40-KristiOSN</v>
       </c>
       <c r="C85" t="str">
         <v/>
@@ -1594,7 +1594,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B86" t="str">
-        <v>LTP-220110-PP-40-LauraOSN</v>
+        <v>LTP-220110-PP-40-LastochkiOSN</v>
       </c>
       <c r="C86" t="str">
         <v/>
@@ -1608,7 +1608,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B87" t="str">
-        <v>LTP-220110-PP-40-LuizaKOMP</v>
+        <v>LTP-220110-PP-40-LauraOSN</v>
       </c>
       <c r="C87" t="str">
         <v/>
@@ -1622,7 +1622,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B88" t="str">
-        <v>LTP-220110-PP-40-LuizaOSN</v>
+        <v>LTP-220110-PP-40-LuizaKOMP</v>
       </c>
       <c r="C88" t="str">
         <v/>
@@ -1636,7 +1636,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B89" t="str">
-        <v>LTP-220110-PP-40-MayskiyDenKOMP</v>
+        <v>LTP-220110-PP-40-LuizaOSN</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1650,7 +1650,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B90" t="str">
-        <v>LTP-220110-PP-40-MayskiyDenOSN</v>
+        <v>LTP-220110-PP-40-MayskiyDenKOMP</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -1664,7 +1664,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B91" t="str">
-        <v>LTP-220110-PP-40-OazisGrayOSN</v>
+        <v>LTP-220110-PP-40-MayskiyDenOSN</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -1678,7 +1678,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B92" t="str">
-        <v>LTP-220110-PP-40-OazisOlivaKOMP</v>
+        <v>LTP-220110-PP-40-OazisGrayOSN</v>
       </c>
       <c r="C92" t="str">
         <v/>
@@ -1692,7 +1692,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B93" t="str">
-        <v>LTP-220110-PP-40-PaporotnikBirAOSN</v>
+        <v>LTP-220110-PP-40-OazisOlivaKOMP</v>
       </c>
       <c r="C93" t="str">
         <v/>
@@ -1706,7 +1706,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B94" t="str">
-        <v>LTP-220110-PP-40-PaporotnikBirBKOMP</v>
+        <v>LTP-220110-PP-40-PaporotnikBirAOSN</v>
       </c>
       <c r="C94" t="str">
         <v/>
@@ -1720,7 +1720,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B95" t="str">
-        <v>LTP-220110-PP-40-PaporotnikGrayAOSN</v>
+        <v>LTP-220110-PP-40-PaporotnikBirBKOMP</v>
       </c>
       <c r="C95" t="str">
         <v/>
@@ -1734,7 +1734,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B96" t="str">
-        <v>LTP-220110-PP-40-PaporotnikGrayBKOMP</v>
+        <v>LTP-220110-PP-40-PaporotnikGrayAOSN</v>
       </c>
       <c r="C96" t="str">
         <v/>
@@ -1748,7 +1748,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B97" t="str">
-        <v>LTP-220110-PP-40-SansaKOMP</v>
+        <v>LTP-220110-PP-40-PaporotnikGrayBKOMP</v>
       </c>
       <c r="C97" t="str">
         <v/>
@@ -1762,7 +1762,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B98" t="str">
-        <v>LTP-220110-PP-40-SansaOSN</v>
+        <v>LTP-220110-PP-40-SansaKOMP</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B99" t="str">
-        <v>LTP-220110-PP-40-SimonaKOMP</v>
+        <v>LTP-220110-PP-40-SansaOSN</v>
       </c>
       <c r="C99" t="str">
         <v/>
@@ -1790,7 +1790,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B100" t="str">
-        <v>LTP-220110-PP-40-SimonaOSN</v>
+        <v>LTP-220110-PP-40-SimonaKOMP</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -1804,7 +1804,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B101" t="str">
-        <v>LTP-220110-PP-40-ViveyaKOMP</v>
+        <v>LTP-220110-PP-40-SimonaOSN</v>
       </c>
       <c r="C101" t="str">
         <v/>
@@ -1818,7 +1818,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B102" t="str">
-        <v>LTP-220110-PP-40-ViveyaOSN</v>
+        <v>LTP-220110-PP-40-ViveyaKOMP</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B103" t="str">
-        <v>LTP-220110-PP-40-ZvezdnyyBrownBKOMP</v>
+        <v>LTP-220110-PP-40-ViveyaOSN</v>
       </c>
       <c r="C103" t="str">
         <v/>
@@ -1846,13 +1846,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B104" t="str">
-        <v>LTP-220110-PP-40-ZvezdnyyOSN</v>
+        <v>LTP-220110-PP-40-ZvezdnyyBrownBKOMP</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -1860,13 +1860,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B105" t="str">
-        <v>LTP-220110-PP-40-ZvezNeboGrayAOSN</v>
+        <v>LTP-220110-PP-40-ZvezdnyyOSN</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1874,7 +1874,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B106" t="str">
-        <v>LTP-220110-PP-40-SledopytyKOMP</v>
+        <v>LTP-220110-PP-40-ZvezNeboGrayAOSN</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -1888,13 +1888,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B107" t="str">
-        <v>LTP-220110-PP-40-BellaPinkOSN</v>
+        <v>LTP-220110-PP-40-SledopytyKOMP</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -1902,13 +1902,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B108" t="str">
-        <v>LTP-220110-PP-40-ZvezdnoeNeboKOMP</v>
+        <v>LTP-220110-PP-40-BellaPinkOSN</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1916,7 +1916,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B109" t="str">
-        <v>LTP-240130-SST-8-Milk</v>
+        <v>LTP-220110-PP-40-ZvezdnoeNeboKOMP</v>
       </c>
       <c r="C109" t="str">
         <v/>
@@ -1930,7 +1930,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B110" t="str">
-        <v>LTP-220115-M-PP-8-Gray</v>
+        <v>LTP-240130-SST-8-Milk</v>
       </c>
       <c r="C110" t="str">
         <v/>
@@ -1944,7 +1944,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B111" t="str">
-        <v>LTP-220115-M-PP-8-Coffee</v>
+        <v>LTP-220115-M-PP-8-Gray</v>
       </c>
       <c r="C111" t="str">
         <v/>
@@ -1958,13 +1958,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B112" t="str">
-        <v>LTP-220115-M-PP-8-GrayGreen</v>
+        <v>LTP-220115-M-PP-8-Coffee</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -1972,7 +1972,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B113" t="str">
-        <v>LTP-220115-M-PP-8-Brusnik</v>
+        <v>LTP-220115-M-PP-8-GrayGreen</v>
       </c>
       <c r="C113" t="str">
         <v/>
@@ -1986,7 +1986,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B114" t="str">
-        <v>LTP-220115-M-PP-8-Gorchica</v>
+        <v>LTP-220115-M-PP-8-Brusnik</v>
       </c>
       <c r="C114" t="str">
         <v/>
@@ -2000,7 +2000,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B115" t="str">
-        <v>LTP-220115-M-PP-8-Pudra</v>
+        <v>LTP-220115-M-PP-8-Gorchica</v>
       </c>
       <c r="C115" t="str">
         <v/>
@@ -2014,7 +2014,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B116" t="str">
-        <v>LTP-220115-M-PP-8-Persik</v>
+        <v>LTP-220115-M-PP-8-Pudra</v>
       </c>
       <c r="C116" t="str">
         <v/>
@@ -2028,7 +2028,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B117" t="str">
-        <v>LTP-220115-M-PP-8-Baklazhan</v>
+        <v>LTP-220115-M-PP-8-Persik</v>
       </c>
       <c r="C117" t="str">
         <v/>
@@ -2042,13 +2042,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B118" t="str">
-        <v>LTP-220115-M-PP-8-GrayBlue</v>
+        <v>LTP-220115-M-PP-8-Baklazhan</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -2056,7 +2056,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B119" t="str">
-        <v>LTP-220115-M-PP-8-Grafit</v>
+        <v>LTP-220115-M-PP-8-GrayBlue</v>
       </c>
       <c r="C119" t="str">
         <v/>
@@ -2070,13 +2070,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B120" t="str">
-        <v>LTP-220115-M-PP-8-Terrakot</v>
+        <v>LTP-220115-M-PP-8-Grafit</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -2084,13 +2084,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B121" t="str">
-        <v>LTP-220115-M-PP-8-LightPink</v>
+        <v>LTP-220115-M-PP-8-Terrakot</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -2098,13 +2098,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B122" t="str">
-        <v>LTP-220115-M-PP-8-Mint</v>
+        <v>LTP-220115-M-PP-8-LightPink</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2112,7 +2112,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B123" t="str">
-        <v>LTP-220115-M-PP-8-Tifani</v>
+        <v>LTP-220115-M-PP-8-Mint</v>
       </c>
       <c r="C123" t="str">
         <v/>
@@ -2126,13 +2126,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B124" t="str">
-        <v>LTP-220115-M-PP-8-DymchatayaRoza</v>
+        <v>LTP-220115-M-PP-8-Tifani</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -2140,7 +2140,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B125" t="str">
-        <v>LTP-220115-M-PP-8-Oliva</v>
+        <v>LTP-220115-M-PP-8-DymchatayaRoza</v>
       </c>
       <c r="C125" t="str">
         <v/>
@@ -2154,7 +2154,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B126" t="str">
-        <v>LTP-220115-M-PP-8-LightBlue</v>
+        <v>LTP-220115-M-PP-8-Oliva</v>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -2168,7 +2168,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B127" t="str">
-        <v>LTP-220115-M-PP-8-Beige</v>
+        <v>LTP-220115-M-PP-8-LightBlue</v>
       </c>
       <c r="C127" t="str">
         <v/>
@@ -2182,13 +2182,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B128" t="str">
-        <v>LTP-220115-M-PP-8-Latte</v>
+        <v>LTP-220115-M-PP-8-Beige</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
@@ -2196,7 +2196,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B129" t="str">
-        <v>LTP-220115-M-PP-8-White</v>
+        <v>LTP-220115-M-PP-8-Latte</v>
       </c>
       <c r="C129" t="str">
         <v/>
@@ -2210,13 +2210,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B130" t="str">
-        <v>LTP-240130-SST-8-Graphit</v>
+        <v>LTP-220115-M-PP-8-White</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -2224,13 +2224,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B131" t="str">
-        <v>LTP-240130-SST-8-GorkShokolad</v>
+        <v>LTP-240130-SST-8-Graphit</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
@@ -2238,7 +2238,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B132" t="str">
-        <v>LTP-240130-SST-8-Indigo</v>
+        <v>LTP-240130-SST-8-GorkShokolad</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -2252,7 +2252,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B133" t="str">
-        <v>LTP-220115-M-PP-8-Milk</v>
+        <v>LTP-240130-SST-8-Indigo</v>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -2266,13 +2266,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B134" t="str">
-        <v>LTP-240130-SST-8-Gray</v>
+        <v>LTP-220115-M-PP-8-Milk</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
@@ -2280,7 +2280,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B135" t="str">
-        <v>LTP-240130-SST-8-MilkShokolad</v>
+        <v>LTP-240130-SST-8-Gray</v>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -2294,7 +2294,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B136" t="str">
-        <v>LTP-240130-SST-8-Beige</v>
+        <v>LTP-240130-SST-8-MilkShokolad</v>
       </c>
       <c r="C136" t="str">
         <v/>
@@ -2308,7 +2308,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B137" t="str">
-        <v>LTP-240130-SST-8-LightBlue</v>
+        <v>LTP-240130-SST-8-Beige</v>
       </c>
       <c r="C137" t="str">
         <v/>
@@ -2322,7 +2322,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B138" t="str">
-        <v>LTP-240130-SST-8-Oliva</v>
+        <v>LTP-240130-SST-8-LightBlue</v>
       </c>
       <c r="C138" t="str">
         <v/>
@@ -2336,13 +2336,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B139" t="str">
-        <v>LTP-240130-SST-8-DimRoza</v>
+        <v>LTP-240130-SST-8-Oliva</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -2350,18 +2350,32 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B140" t="str">
+        <v>LTP-240130-SST-8-DimRoza</v>
+      </c>
+      <c r="C140" t="str">
+        <v/>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>СЦ (Коляново) (1020002072018000)</v>
+      </c>
+      <c r="B141" t="str">
         <v>LTP-240130-SST-8-SirenTuman</v>
       </c>
-      <c r="C140" t="str">
-        <v/>
-      </c>
-      <c r="D140">
+      <c r="C141" t="str">
+        <v/>
+      </c>
+      <c r="D141">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D141"/>
   </ignoredErrors>
 </worksheet>
 </file>